--- a/public/downloads/Import_cong_viec_GV.xlsx
+++ b/public/downloads/Import_cong_viec_GV.xlsx
@@ -524,13 +524,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="3"/>
+    <col width="46" customWidth="1" min="2" max="3"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" style="7" min="4" max="5"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="11"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -621,17 +621,17 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Soạn Kế hoạch bài dạy (giáo án) đúng chuẩn Công văn 5512/BGDĐT, tích hợp năng lực số và ứng dụng AI</t>
+          <t>Hoàn thành chấm bài, vào điểm, tổng kết đánh giá xếp loại học sinh cuối năm học 2025 - 2026 trên phần mềm VnEdu</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>N1_550 - Soạn thảo văn bản hành chính</t>
+          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -645,7 +645,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Giáo án điện tử môn giảng dạy lưu trên hệ thống CSDL trường</t>
+          <t>Sổ điểm điện tử năm học 2025-2026 trên hệ thống VnEdu</t>
         </is>
       </c>
     </row>
@@ -655,17 +655,17 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng Kế hoạch dạy học môn học cá nhân và kế hoạch kiểm tra đánh giá định kỳ theo phân phối chương trình</t>
+          <t>Thực hiện nhiệm vụ coi thi, chấm thi kỳ thi tuyển sinh lớp 10 THPT và kỳ thi tốt nghiệp THPT năm 2026 theo điều động của Sở</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>N1_550 - Soạn thảo văn bản hành chính</t>
+          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
@@ -679,27 +679,27 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>KHDH cá nhân đã được Tổ trưởng và BGH phê duyệt</t>
+          <t>Quyết định điều động cán bộ coi thi, chấm thi của Sở GD&amp;ĐT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Thiết kế học liệu số, bài giảng điện tử tương tác và ngân hàng câu hỏi trắc nghiệm rèn luyện trực tuyến</t>
+          <t>Hoàn thiện hồ sơ sáng kiến kinh nghiệm, hồ sơ minh chứng đề nghị đánh giá xếp loại viên chức cuối năm học 2025 - 2026</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>N1_550 - Soạn thảo văn bản hành chính</t>
+          <t>N3_658 - Thẩm định hồ sơ và tham mưu công tác sáng kiến, đề tài nghiên cứu khoa học; các cuộc thi về công tác học sinh sinh viên; hồ sơ b</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Kho bài giảng điện tử và link học liệu số trên cổng web trường</t>
+          <t>Báo cáo sáng kiến kinh nghiệm và phiếu tự đánh giá viên chức</t>
         </is>
       </c>
     </row>
@@ -723,17 +723,17 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Thực hiện đầy đủ, nghiêm túc số tiết dạy theo phân công thời khóa biểu; lên lớp đúng giờ, không bỏ tiết</t>
+          <t>Tham gia đầy đủ lớp bồi dưỡng chính trị hè năm 2026 và hoàn thành bài thu hoạch đạt yêu cầu</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Sổ đầu bài các lớp, sổ theo dõi chuyên môn của tổ</t>
+          <t>Bài thu hoạch bồi dưỡng chính trị hè 2026</t>
         </is>
       </c>
     </row>
@@ -757,17 +757,17 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Tích cực đổi mới phương pháp dạy học, phát huy tính tích cực, chủ động, sáng tạo và năng lực tự học của học sinh</t>
+          <t>Hoàn thành khóa tập huấn chuyên môn, bồi dưỡng SGK và đổi mới phương pháp dạy học theo CT GDPT 2018 trong hè</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
@@ -781,27 +781,27 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Phiếu đánh giá tiết dạy đạt loại Khá, Giỏi</t>
+          <t>Giấy chứng nhận / kết quả hoàn thành tập huấn bồi dưỡng hè 2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Tham gia đầy đủ các buổi sinh hoạt chuyên môn của tổ theo định hướng nghiên cứu bài học (tối thiểu 2 lần/tháng)</t>
+          <t>Xây dựng Kế hoạch dạy học môn học cá nhân năm học 2026 - 2027 nộp Tổ trưởng chuyên môn phê duyệt</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+          <t>N1_550 - Soạn thảo văn bản hành chính</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
@@ -815,27 +815,27 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Biên bản sinh hoạt tổ chuyên môn</t>
+          <t>Kế hoạch dạy học cá nhân năm học 2026-2027 có xác nhận của Tổ trưởng</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Thực hiện dự giờ đồng nghiệp đúng quy định (đạt 18-20 tiết/năm), trao đổi, rút kinh nghiệm chuyên môn</t>
+          <t>Nhận lớp chủ nhiệm, tổ chức cho học sinh tựu trường, ổn định tổ chức lớp và phổ biến nội quy học sinh</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
@@ -849,27 +849,27 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Sổ dự giờ của giáo viên có đầy đủ nhận xét, xếp loại</t>
+          <t>Biên bản họp lớp đầu năm và danh sách ban cán sự lớp</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng ma trận, bản đặc tả và đề kiểm tra định kỳ (giữa kỳ, cuối kỳ) theo đúng định hướng đánh giá năng lực</t>
+          <t>Chuẩn bị trang phục, hướng dẫn học sinh tham gia Lễ Khai giảng năm học 2026 - 2027 trang nghiêm, đầy đủ quân số</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
+          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
@@ -883,27 +883,27 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Hồ sơ ngân hàng đề kiểm tra nộp tổ chuyên môn</t>
+          <t>Sổ chủ nhiệm ghi nhận quân số dự Khai giảng 100%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Chấm bài kiểm tra chính xác, trả bài kịp thời; cập nhật điểm số thường xuyên và định kỳ đầy đủ lên VnEdu</t>
+          <t>Tổ chức Hội nghị Ban đại diện Cha mẹ học sinh lớp đầu năm học 2026 - 2027; lập biên bản họp đúng quy định</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
+          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
@@ -917,27 +917,27 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Sổ điểm điện tử trên VnEdu đúng tiến độ theo từng mốc thời gian</t>
+          <t>Biên bản họp phụ huynh học sinh đầu năm học 2026-2027</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Tham gia công tác coi thi, chấm thi kiểm tra định kỳ, thi thử tốt nghiệp THPT an toàn, nghiêm túc, đúng quy chế</t>
+          <t>Cập nhật hồ sơ học sinh, hoàn thiện cơ sở dữ liệu lý lịch và thông tin liên lạc của học sinh trên hệ thống VnEdu</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
+          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
@@ -951,27 +951,27 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Bảng tổng hợp điểm chấm thi và biên bản coi thi</t>
+          <t>Dữ liệu hồ sơ học sinh lớp chủ nhiệm trên hệ thống CSDL trường</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Phát hiện, lập danh sách và trực tiếp tham gia bồi dưỡng đội tuyển học sinh giỏi môn phụ trách thi cấp trường, cấp tỉnh</t>
+          <t>Soạn Kế hoạch bài dạy (giáo án) các tuần học tháng 9/2026 đúng chuẩn Công văn 5512/BGDĐT, tích hợp năng lực số và AI</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">N2_1108 - Tổ chức kỳ thi chọn Đội tuyển tham dự kỳ thi chọn học sinh giỏi quốc gia THPT năm học 2026 - 2027 (tổ chức ra đề, coi thi, chấm </t>
+          <t>N1_550 - Soạn thảo văn bản hành chính</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>30/03/2027</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
@@ -985,27 +985,27 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch bồi dưỡng HSG và kết quả thi HSG cấp tỉnh</t>
+          <t>Giáo án các tuần 1, 2, 3, 4 tháng 9 lưu trên hệ thống CSDL giáo án</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng kế hoạch và tổ chức dạy phụ đạo, giúp đỡ học sinh học lực yếu kém, có nguy cơ không đạt chuẩn</t>
+          <t>Thiết kế bài giảng điện tử và học liệu số tương tác phục vụ dạy học các chuyên đề đầu năm học mới</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">N2_1108 - Tổ chức kỳ thi chọn Đội tuyển tham dự kỳ thi chọn học sinh giỏi quốc gia THPT năm học 2026 - 2027 (tổ chức ra đề, coi thi, chấm </t>
+          <t>N1_550 - Soạn thảo văn bản hành chính</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>20/05/2027</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch phụ đạo học sinh yếu kém và theo dõi sự tiến bộ</t>
+          <t>Link bài giảng điện tử và học liệu số tải lên thư viện trường</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Viết sáng kiến kinh nghiệm hoặc giải pháp đổi mới giáo dục được Hội đồng chuyên môn nhà trường nghiệm thu đạt loại Khá trở lên</t>
+          <t>Thực hiện nghiêm túc thời khóa biểu tháng 9/2026, lên lớp đúng giờ, duy trì tốt nền nếp và kỷ luật dạy học</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>N3_658 - Thẩm định hồ sơ và tham mưu công tác sáng kiến, đề tài nghiên cứu khoa học; các cuộc thi về công tác học sinh sinh viên; hồ sơ b</t>
+          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>15/04/2027</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Văn bản báo cáo sáng kiến kinh nghiệm năm học 2026-2027</t>
+          <t>Sổ đầu bài các lớp giảng dạy tháng 9/2026</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn học sinh tham gia Cuộc thi Khoa học kỹ thuật (KHKT) cấp trường/cấp tỉnh hoặc các cuộc thi trí tuệ</t>
+          <t>Tham gia các buổi sinh hoạt tổ chuyên môn đầu năm học: thống nhất ma trận đề, kế hoạch giáo dục và quy chế tổ</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>N3_658 - Thẩm định hồ sơ và tham mưu công tác sáng kiến, đề tài nghiên cứu khoa học; các cuộc thi về công tác học sinh sinh viên; hồ sơ b</t>
+          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>15/01/2027</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Dự án dự thi KHKT học sinh và Quyết định công nhận</t>
+          <t>Biên bản họp tổ chuyên môn tháng 9/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng kế hoạch chủ nhiệm lớp, nắm vững hoàn cảnh từng học sinh; duy trì sĩ số lớp 100%, phòng chống bỏ học</t>
+          <t>Thực hiện dự giờ đồng nghiệp tháng 9 theo kế hoạch tổ chuyên môn (đạt 2 tiết/tháng), trao đổi kinh nghiệm sư phạm</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
+          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>28/09/2026</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Sổ công tác chủ nhiệm lớp, biên bản thăm gia đình học sinh</t>
+          <t>Sổ dự giờ giáo viên có nhận xét và đánh giá tiết dạy</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Tổ chức sinh hoạt lớp, giáo dục đạo đức, kỹ năng sống, văn hóa ứng xử học đường và phòng chống bạo lực học đường</t>
+          <t>Thực hiện kiểm tra đánh giá thường xuyên học sinh theo đúng kế hoạch; chấm bài và vào điểm VnEdu kịp thời</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
+          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Giáo án tiết sinh hoạt lớp theo chủ đề hàng tuần</t>
+          <t>Điểm kiểm tra thường xuyên tháng 9 cập nhật trên VnEdu</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Tổ chức các buổi họp phụ huynh học sinh đầu năm, giữa kỳ, cuối năm; giữ mối liên lạc chặt chẽ với cha mẹ học sinh qua Zalo/Smas</t>
+          <t>Khảo sát chất lượng đầu năm, phát hiện và lập danh sách học sinh năng khiếu để bồi dưỡng đội tuyển HSG môn phụ trách</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
+          <t xml:space="preserve">N2_1108 - Tổ chức kỳ thi chọn Đội tuyển tham dự kỳ thi chọn học sinh giỏi quốc gia THPT năm học 2026 - 2027 (tổ chức ra đề, coi thi, chấm </t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
@@ -1189,27 +1189,27 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Biên bản họp Ban đại diện cha mẹ học sinh lớp</t>
+          <t>Danh sách đội tuyển HSG và Kế hoạch bồi dưỡng HSG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Đánh giá, nhận xét rèn luyện và học tập của học sinh; cập nhật kết quả hạnh kiểm, khen thưởng đầy đủ lên phần mềm CSDL</t>
+          <t>Lập danh sách học sinh học lực yếu kém đầu năm học để xây dựng phương án dạy phụ đạo, kèm cặp nâng cao chất lượng</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
+          <t xml:space="preserve">N2_1108 - Tổ chức kỳ thi chọn Đội tuyển tham dự kỳ thi chọn học sinh giỏi quốc gia THPT năm học 2026 - 2027 (tổ chức ra đề, coi thi, chấm </t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
@@ -1223,27 +1223,27 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Hồ sơ đánh giá rèn luyện học kỳ 1, học kỳ 2 trên VnEdu</t>
+          <t>Kế hoạch phụ đạo học sinh có kết quả khảo sát đầu năm thấp</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Tham gia đầy đủ các lớp bồi dưỡng thường xuyên, bồi dưỡng chuyên môn nghiệp vụ theo quy định của Sở GD&amp;ĐT</t>
+          <t>Đăng ký tên đề tài Sáng kiến kinh nghiệm hoặc Đề tài nghiên cứu khoa học sư phạm ứng dụng năm học 2026 - 2027</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
+          <t>N3_658 - Thẩm định hồ sơ và tham mưu công tác sáng kiến, đề tài nghiên cứu khoa học; các cuộc thi về công tác học sinh sinh viên; hồ sơ b</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận bồi dưỡng thường xuyên hoặc kết quả trên cổng bồi dưỡng</t>
+          <t>Phiếu đăng ký đề tài SKKN năm học 2026-2027 nộp Tổ chuyên môn</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Tự bồi dưỡng nâng cao trình độ chuyên môn, năng lực ứng dụng CNTT, ngoại ngữ và kỹ năng sư phạm hiện đại</t>
+          <t>Xây dựng Kế hoạch tự bồi dưỡng thường xuyên cá nhân năm học 2026 - 2027 theo quy định của Bộ và Sở GD&amp;ĐT</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>31/05/2027</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch tự học và bài thu hoạch bồi dưỡng thường xuyên cá nhân</t>
+          <t>Bản kế hoạch tự học, bồi dưỡng thường xuyên năm học 2026-2027</t>
         </is>
       </c>
     </row>

--- a/public/downloads/Import_cong_viec_GV.xlsx
+++ b/public/downloads/Import_cong_viec_GV.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Mẫu import" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SPCV" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mẫu import" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPCV" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L75"/>
+  <dimension ref="A2:L199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -621,17 +621,17 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Hoàn thành chấm bài, vào điểm, tổng kết đánh giá xếp loại học sinh cuối năm học 2025 - 2026 trên phần mềm VnEdu</t>
+          <t>Hoàn thành nội dung chương trình giảng dạy học kỳ II theo phân phối chương trình, bảo đảm đúng tiến độ quy định</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
+          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
@@ -645,17 +645,17 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Sổ điểm điện tử năm học 2025-2026 trên hệ thống VnEdu</t>
+          <t>Sổ ghi đầu bài các lớp hoàn thành chương trình tuần 35</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Thực hiện nhiệm vụ coi thi, chấm thi kỳ thi tuyển sinh lớp 10 THPT và kỳ thi tốt nghiệp THPT năm 2026 theo điều động của Sở</t>
+          <t>Thực hiện ra đề, coi thi, chấm bài kiểm tra cuối học kỳ II theo đúng ma trận đặc tả; nhập điểm đầy đủ lên VnEdu</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
@@ -679,7 +679,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Quyết định điều động cán bộ coi thi, chấm thi của Sở GD&amp;ĐT</t>
+          <t>Bảng điểm kiểm tra cuối học kỳ II trên hệ thống VnEdu</t>
         </is>
       </c>
     </row>
@@ -689,17 +689,17 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Hoàn thiện hồ sơ sáng kiến kinh nghiệm, hồ sơ minh chứng đề nghị đánh giá xếp loại viên chức cuối năm học 2025 - 2026</t>
+          <t>Thực hiện coi thi, chấm thi thử tốt nghiệp THPT 2026 môn phụ trách, hướng dẫn học sinh sửa bài và ôn tập củng cố kiến thức</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>N3_658 - Thẩm định hồ sơ và tham mưu công tác sáng kiến, đề tài nghiên cứu khoa học; các cuộc thi về công tác học sinh sinh viên; hồ sơ b</t>
+          <t>N2_1091 - Tổ chức thi thử tốt nghiệp THPT năm 2026 (ra đề, in sao đề thi)</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Báo cáo sáng kiến kinh nghiệm và phiếu tự đánh giá viên chức</t>
+          <t>Bảng phân tích kết quả bài thi thử của học sinh</t>
         </is>
       </c>
     </row>
@@ -723,17 +723,17 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Tham gia đầy đủ lớp bồi dưỡng chính trị hè năm 2026 và hoàn thành bài thu hoạch đạt yêu cầu</t>
+          <t>Hoàn thành đánh giá xếp loại học lực, hạnh kiểm/kết quả học tập và rèn luyện của học sinh lớp chủ nhiệm cuối năm trên VnEdu</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
+          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Bài thu hoạch bồi dưỡng chính trị hè 2026</t>
+          <t>Sổ tổng hợp kết quả đánh giá học sinh năm học 2025-2026</t>
         </is>
       </c>
     </row>
@@ -757,17 +757,17 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Hoàn thành khóa tập huấn chuyên môn, bồi dưỡng SGK và đổi mới phương pháp dạy học theo CT GDPT 2018 trong hè</t>
+          <t>Tổ chức họp Ban đại diện Cha mẹ học sinh lớp cuối năm học 2025 - 2026, thông báo kết quả học tập và phối hợp quản lý học sinh hè</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
+          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Giấy chứng nhận / kết quả hoàn thành tập huấn bồi dưỡng hè 2026</t>
+          <t>Biên bản họp phụ huynh học sinh cuối năm học 2025-2026</t>
         </is>
       </c>
     </row>
@@ -791,17 +791,17 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng Kế hoạch dạy học môn học cá nhân năm học 2026 - 2027 nộp Tổ trưởng chuyên môn phê duyệt</t>
+          <t>Hoàn thiện báo cáo kết quả thực hiện Sáng kiến kinh nghiệm / Đề tài NCKH sư phạm ứng dụng năm học 2025 - 2026 nộp Hội đồng cơ sở</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>N1_550 - Soạn thảo văn bản hành chính</t>
+          <t>N3_658 - Thẩm định hồ sơ và tham mưu công tác sáng kiến, đề tài nghiên cứu khoa học; các cuộc thi về công tác học sinh sinh viên; hồ sơ b</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
@@ -815,7 +815,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch dạy học cá nhân năm học 2026-2027 có xác nhận của Tổ trưởng</t>
+          <t>Bản báo cáo kết quả đề tài sáng kiến kinh nghiệm cá nhân</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Nhận lớp chủ nhiệm, tổ chức cho học sinh tựu trường, ổn định tổ chức lớp và phổ biến nội quy học sinh</t>
+          <t>Tự đánh giá Chuẩn nghề nghiệp giáo viên cơ sở giáo dục phổ thông năm học 2025 - 2026 theo Thông tư 20/2018/TT-BGDĐT và cập nhật TEMIS</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
+          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Biên bản họp lớp đầu năm và danh sách ban cán sự lớp</t>
+          <t>Phiếu tự đánh giá Chuẩn nghề nghiệp giáo viên trên hệ thống TEMIS</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Chuẩn bị trang phục, hướng dẫn học sinh tham gia Lễ Khai giảng năm học 2026 - 2027 trang nghiêm, đầy đủ quân số</t>
+          <t>Hoàn thành chấm bài, vào điểm, tổng kết đánh giá xếp loại học sinh cuối năm học 2025 - 2026 trên phần mềm VnEdu</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
+          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Sổ chủ nhiệm ghi nhận quân số dự Khai giảng 100%</t>
+          <t>Sổ điểm điện tử năm học 2025-2026 trên hệ thống VnEdu</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Tổ chức Hội nghị Ban đại diện Cha mẹ học sinh lớp đầu năm học 2026 - 2027; lập biên bản họp đúng quy định</t>
+          <t>Thực hiện nhiệm vụ coi thi, chấm thi kỳ thi tuyển sinh lớp 10 THPT và kỳ thi tốt nghiệp THPT năm 2026 theo điều động của Sở</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
+          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
@@ -917,27 +917,27 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Biên bản họp phụ huynh học sinh đầu năm học 2026-2027</t>
+          <t>Quyết định điều động cán bộ coi thi, chấm thi của Sở GD&amp;ĐT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật hồ sơ học sinh, hoàn thiện cơ sở dữ liệu lý lịch và thông tin liên lạc của học sinh trên hệ thống VnEdu</t>
+          <t>Hoàn thiện hồ sơ sáng kiến kinh nghiệm, hồ sơ minh chứng đề nghị đánh giá xếp loại viên chức cuối năm học 2025 - 2026</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
+          <t>N3_658 - Thẩm định hồ sơ và tham mưu công tác sáng kiến, đề tài nghiên cứu khoa học; các cuộc thi về công tác học sinh sinh viên; hồ sơ b</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Dữ liệu hồ sơ học sinh lớp chủ nhiệm trên hệ thống CSDL trường</t>
+          <t>Báo cáo sáng kiến kinh nghiệm và phiếu tự đánh giá viên chức</t>
         </is>
       </c>
     </row>
@@ -961,17 +961,17 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Soạn Kế hoạch bài dạy (giáo án) các tuần học tháng 9/2026 đúng chuẩn Công văn 5512/BGDĐT, tích hợp năng lực số và AI</t>
+          <t>Tham gia đầy đủ lớp bồi dưỡng chính trị hè năm 2026 và hoàn thành bài thu hoạch đạt yêu cầu</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>N1_550 - Soạn thảo văn bản hành chính</t>
+          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>Giáo án các tuần 1, 2, 3, 4 tháng 9 lưu trên hệ thống CSDL giáo án</t>
+          <t>Bài thu hoạch bồi dưỡng chính trị hè 2026</t>
         </is>
       </c>
     </row>
@@ -995,17 +995,17 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Thiết kế bài giảng điện tử và học liệu số tương tác phục vụ dạy học các chuyên đề đầu năm học mới</t>
+          <t>Hoàn thành khóa tập huấn chuyên môn, bồi dưỡng SGK và đổi mới phương pháp dạy học theo CT GDPT 2018 trong hè</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>N1_550 - Soạn thảo văn bản hành chính</t>
+          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>20/09/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Link bài giảng điện tử và học liệu số tải lên thư viện trường</t>
+          <t>Giấy chứng nhận / kết quả hoàn thành tập huấn bồi dưỡng hè 2026</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Thực hiện nghiêm túc thời khóa biểu tháng 9/2026, lên lớp đúng giờ, duy trì tốt nền nếp và kỷ luật dạy học</t>
+          <t>Xây dựng Kế hoạch dạy học môn học cá nhân năm học 2026 - 2027 nộp Tổ trưởng chuyên môn phê duyệt</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+          <t>N1_550 - Soạn thảo văn bản hành chính</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
@@ -1053,27 +1053,27 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Sổ đầu bài các lớp giảng dạy tháng 9/2026</t>
+          <t>Kế hoạch dạy học cá nhân năm học 2026-2027 có xác nhận của Tổ trưởng</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Tham gia các buổi sinh hoạt tổ chuyên môn đầu năm học: thống nhất ma trận đề, kế hoạch giáo dục và quy chế tổ</t>
+          <t>Nhận lớp chủ nhiệm, tổ chức cho học sinh tựu trường, ổn định tổ chức lớp và phổ biến nội quy học sinh</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
@@ -1087,27 +1087,27 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Biên bản họp tổ chuyên môn tháng 9/2026</t>
+          <t>Biên bản họp lớp đầu năm và danh sách ban cán sự lớp</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Thực hiện dự giờ đồng nghiệp tháng 9 theo kế hoạch tổ chuyên môn (đạt 2 tiết/tháng), trao đổi kinh nghiệm sư phạm</t>
+          <t>Chuẩn bị trang phục, hướng dẫn học sinh tham gia Lễ Khai giảng năm học 2026 - 2027 trang nghiêm, đầy đủ quân số</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
@@ -1121,27 +1121,27 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Sổ dự giờ giáo viên có nhận xét và đánh giá tiết dạy</t>
+          <t>Sổ chủ nhiệm ghi nhận quân số dự Khai giảng 100%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Thực hiện kiểm tra đánh giá thường xuyên học sinh theo đúng kế hoạch; chấm bài và vào điểm VnEdu kịp thời</t>
+          <t>Tổ chức Hội nghị Ban đại diện Cha mẹ học sinh lớp đầu năm học 2026 - 2027; lập biên bản họp đúng quy định</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
+          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Điểm kiểm tra thường xuyên tháng 9 cập nhật trên VnEdu</t>
+          <t>Biên bản họp phụ huynh học sinh đầu năm học 2026-2027</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Khảo sát chất lượng đầu năm, phát hiện và lập danh sách học sinh năng khiếu để bồi dưỡng đội tuyển HSG môn phụ trách</t>
+          <t>Cập nhật hồ sơ học sinh, hoàn thiện cơ sở dữ liệu lý lịch và thông tin liên lạc của học sinh trên hệ thống VnEdu</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">N2_1108 - Tổ chức kỳ thi chọn Đội tuyển tham dự kỳ thi chọn học sinh giỏi quốc gia THPT năm học 2026 - 2027 (tổ chức ra đề, coi thi, chấm </t>
+          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Danh sách đội tuyển HSG và Kế hoạch bồi dưỡng HSG</t>
+          <t>Dữ liệu hồ sơ học sinh lớp chủ nhiệm trên hệ thống CSDL trường</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Lập danh sách học sinh học lực yếu kém đầu năm học để xây dựng phương án dạy phụ đạo, kèm cặp nâng cao chất lượng</t>
+          <t>Soạn Kế hoạch bài dạy (giáo án) các tuần học tháng 9/2026 đúng chuẩn Công văn 5512/BGDĐT, tích hợp năng lực số và AI</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">N2_1108 - Tổ chức kỳ thi chọn Đội tuyển tham dự kỳ thi chọn học sinh giỏi quốc gia THPT năm học 2026 - 2027 (tổ chức ra đề, coi thi, chấm </t>
+          <t>N1_550 - Soạn thảo văn bản hành chính</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
@@ -1223,27 +1223,27 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Kế hoạch phụ đạo học sinh có kết quả khảo sát đầu năm thấp</t>
+          <t>Giáo án các tuần 1, 2, 3, 4 tháng 9 lưu trên hệ thống CSDL giáo án</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Đăng ký tên đề tài Sáng kiến kinh nghiệm hoặc Đề tài nghiên cứu khoa học sư phạm ứng dụng năm học 2026 - 2027</t>
+          <t>Thiết kế bài giảng điện tử và học liệu số tương tác phục vụ dạy học các chuyên đề đầu năm học mới</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>N3_658 - Thẩm định hồ sơ và tham mưu công tác sáng kiến, đề tài nghiên cứu khoa học; các cuộc thi về công tác học sinh sinh viên; hồ sơ b</t>
+          <t>N1_550 - Soạn thảo văn bản hành chính</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Phiếu đăng ký đề tài SKKN năm học 2026-2027 nộp Tổ chuyên môn</t>
+          <t>Link bài giảng điện tử và học liệu số tải lên thư viện trường</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng Kế hoạch tự bồi dưỡng thường xuyên cá nhân năm học 2026 - 2027 theo quy định của Bộ và Sở GD&amp;ĐT</t>
+          <t>Thực hiện nghiêm túc thời khóa biểu tháng 9/2026, lên lớp đúng giờ, duy trì tốt nền nếp và kỷ luật dạy học</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
+          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
@@ -1291,79 +1291,247 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
+          <t>Sổ đầu bài các lớp giảng dạy tháng 9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Tham gia các buổi sinh hoạt tổ chuyên môn đầu năm học: thống nhất ma trận đề, kế hoạch giáo dục và quy chế tổ</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Biên bản họp tổ chuyên môn tháng 9/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Thực hiện dự giờ đồng nghiệp tháng 9 theo kế hoạch tổ chuyên môn (đạt 2 tiết/tháng), trao đổi kinh nghiệm sư phạm</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Sổ dự giờ giáo viên có nhận xét và đánh giá tiết dạy</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Thực hiện kiểm tra đánh giá thường xuyên học sinh theo đúng kế hoạch; chấm bài và vào điểm VnEdu kịp thời</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Điểm kiểm tra thường xuyên tháng 9 cập nhật trên VnEdu</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Khảo sát chất lượng đầu năm, phát hiện và lập danh sách học sinh năng khiếu để bồi dưỡng đội tuyển HSG môn phụ trách</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N2_1108 - Tổ chức kỳ thi chọn Đội tuyển tham dự kỳ thi chọn học sinh giỏi quốc gia THPT năm học 2026 - 2027 (tổ chức ra đề, coi thi, chấm </t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Danh sách đội tuyển HSG và Kế hoạch bồi dưỡng HSG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Lập danh sách học sinh học lực yếu kém đầu năm học để xây dựng phương án dạy phụ đạo, kèm cặp nâng cao chất lượng</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N2_1108 - Tổ chức kỳ thi chọn Đội tuyển tham dự kỳ thi chọn học sinh giỏi quốc gia THPT năm học 2026 - 2027 (tổ chức ra đề, coi thi, chấm </t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Kế hoạch phụ đạo học sinh có kết quả khảo sát đầu năm thấp</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Đăng ký tên đề tài Sáng kiến kinh nghiệm hoặc Đề tài nghiên cứu khoa học sư phạm ứng dụng năm học 2026 - 2027</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>N3_658 - Thẩm định hồ sơ và tham mưu công tác sáng kiến, đề tài nghiên cứu khoa học; các cuộc thi về công tác học sinh sinh viên; hồ sơ b</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Phiếu đăng ký đề tài SKKN năm học 2026-2027 nộp Tổ chuyên môn</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Xây dựng Kế hoạch tự bồi dưỡng thường xuyên cá nhân năm học 2026 - 2027 theo quy định của Bộ và Sở GD&amp;ĐT</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
           <t>Bản kế hoạch tự học, bồi dưỡng thường xuyên năm học 2026-2027</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="10" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="10" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="10" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="10" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="10" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="n"/>
@@ -1765,6 +1933,337 @@
       <c r="G75" s="9" t="n"/>
       <c r="H75" s="10" t="n"/>
     </row>
+    <row r="76">
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="9" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="9" t="n"/>
+      <c r="G76" s="9" t="n"/>
+      <c r="H76" s="10" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="9" t="n"/>
+      <c r="H77" s="10" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="9" t="n"/>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="9" t="n"/>
+      <c r="G78" s="9" t="n"/>
+      <c r="H78" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="9" t="n"/>
+      <c r="E79" s="9" t="n"/>
+      <c r="F79" s="9" t="n"/>
+      <c r="G79" s="9" t="n"/>
+      <c r="H79" s="10" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="10" t="n"/>
+      <c r="C80" s="10" t="n"/>
+      <c r="D80" s="9" t="n"/>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="9" t="n"/>
+      <c r="G80" s="9" t="n"/>
+      <c r="H80" s="10" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="9" t="n"/>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="9" t="n"/>
+      <c r="G81" s="9" t="n"/>
+      <c r="H81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="9" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="9" t="n"/>
+      <c r="G82" s="9" t="n"/>
+      <c r="H82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n"/>
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="9" t="n"/>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="9" t="n"/>
+      <c r="G83" s="9" t="n"/>
+      <c r="H83" s="10" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="10" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="9" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="9" t="n"/>
+      <c r="G84" s="9" t="n"/>
+      <c r="H84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="10" t="n"/>
+      <c r="D85" s="9" t="n"/>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="9" t="n"/>
+      <c r="H85" s="10" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="9" t="n"/>
+      <c r="E86" s="9" t="n"/>
+      <c r="F86" s="9" t="n"/>
+      <c r="G86" s="9" t="n"/>
+      <c r="H86" s="10" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="9" t="n"/>
+      <c r="F87" s="9" t="n"/>
+      <c r="G87" s="9" t="n"/>
+      <c r="H87" s="10" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="9" t="n"/>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="9" t="n"/>
+      <c r="G88" s="9" t="n"/>
+      <c r="H88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n"/>
+      <c r="B89" s="10" t="n"/>
+      <c r="C89" s="10" t="n"/>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="9" t="n"/>
+      <c r="H89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="9" t="n"/>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="9" t="n"/>
+      <c r="G90" s="9" t="n"/>
+      <c r="H90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n"/>
+      <c r="B91" s="10" t="n"/>
+      <c r="C91" s="10" t="n"/>
+      <c r="D91" s="9" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="9" t="n"/>
+      <c r="H91" s="10" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n"/>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="9" t="n"/>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="9" t="n"/>
+      <c r="H92" s="10" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n"/>
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="10" t="n"/>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="9" t="n"/>
+      <c r="H93" s="10" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="10" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="10" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n"/>
+      <c r="B95" s="10" t="n"/>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="9" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="9" t="n"/>
+      <c r="H95" s="10" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="10" t="n"/>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="9" t="n"/>
+      <c r="H96" s="10" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="10" t="n"/>
+      <c r="C97" s="10" t="n"/>
+      <c r="D97" s="9" t="n"/>
+      <c r="E97" s="9" t="n"/>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="9" t="n"/>
+      <c r="H97" s="10" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="10" t="n"/>
+      <c r="C98" s="10" t="n"/>
+      <c r="D98" s="9" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="9" t="n"/>
+      <c r="H98" s="10" t="n"/>
+    </row>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:L2"/>

--- a/public/downloads/Import_cong_viec_GV.xlsx
+++ b/public/downloads/Import_cong_viec_GV.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L199"/>
+  <dimension ref="A2:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1534,736 +1534,413 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="10" t="n"/>
+      <c r="A36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Thực hiện giảng dạy đảm bảo tiến độ chương trình tháng 10, soạn bài đầy đủ theo CV 5512, sử dụng đồ dùng dạy học và ứng dụng CNTT hiệu quả</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Giáo án điện tử tháng 10 và sổ ghi đầu bài đảm bảo tiến độ</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="10" t="n"/>
+      <c r="A37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Ra đề, coi thi, chấm bài kiểm tra giữa học kỳ I theo ma trận đặc tả đã xây dựng; nhập điểm đầy đủ lên VnEdu đúng hạn</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Đề kiểm tra giữa HKI có ma trận, bảng điểm cập nhật VnEdu</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="10" t="n"/>
+      <c r="A38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Thực hiện sinh hoạt tổ chuyên môn tháng 10 theo chủ đề đổi mới phương pháp dạy học, nghiên cứu bài học và ứng dụng AI</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Biên bản sinh hoạt tổ chuyên môn tháng 10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="n"/>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="10" t="n"/>
+      <c r="A39" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Dự giờ đồng nghiệp đạt ít nhất 2 tiết/tháng, ghi nhận xét cụ thể và trao đổi phương pháp dạy học sau tiết dự giờ</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Sổ dự giờ tháng 10 có nhận xét chi tiết và chữ ký</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="9" t="n"/>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="10" t="n"/>
+      <c r="A40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Tiếp tục bồi dưỡng học sinh giỏi môn phụ trách; tổ chức phụ đạo học sinh yếu kém đầu năm theo kế hoạch đã lập</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N2_1108 - Tổ chức kỳ thi chọn Đội tuyển tham dự kỳ thi chọn học sinh giỏi quốc gia THPT năm học 2026 - 2027 (tổ chức ra đề, coi thi, chấm </t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Sổ bồi dưỡng HSG và danh sách học sinh tham gia phụ đạo tháng 10</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="n"/>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="10" t="n"/>
+      <c r="A41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Theo dõi, đánh giá nền nếp lớp chủ nhiệm tháng 10; tổ chức sinh hoạt lớp, họp lớp phân tích kết quả kiểm tra giữa kỳ</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>N1_565 - Quản lý, cập nhật cơ sở dữ liệu học sinh</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Sổ chủ nhiệm tháng 10/2026 và biên bản sinh hoạt lớp</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="n"/>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="10" t="n"/>
+      <c r="A42" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Thực hiện kiểm tra đánh giá thường xuyên đúng kế hoạch; chấm bài, trả bài, nhận xét cụ thể và vào điểm VnEdu kịp thời</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>N1_564 - Quản lý dữ liệu của các Kỳ thi</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>Điểm kiểm tra thường xuyên tháng 10 cập nhật trên VnEdu</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="10" t="n"/>
+      <c r="A43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Đăng ký và tham gia tiết dạy mẫu, tiết dạy tốt chào mừng Ngày Nhà giáo Việt Nam 20/11; đăng ký thi giáo viên dạy giỏi cấp trường</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>N3_658 - Thẩm định hồ sơ và tham mưu công tác sáng kiến, đề tài nghiên cứu khoa học; các cuộc thi về công tác học sinh sinh viên; hồ sơ b</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Phiếu đăng ký thi GV dạy giỏi và đề cương tiết dạy mẫu</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="10" t="n"/>
+      <c r="A44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Triển khai các nội dung bồi dưỡng thường xuyên tháng 10 theo kế hoạch cá nhân đã đăng ký; ghi nhật ký bồi dưỡng đầy đủ</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>N3_652 - Xây dựng Kế hoạch đào tạo, bồi dưỡng công chức, viên chức</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>Nhật ký tự bồi dưỡng thường xuyên tháng 10/2026</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="n"/>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="10" t="n"/>
+      <c r="A45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Tham gia đầy đủ các buổi họp tổ chuyên môn, họp Hội đồng sư phạm tháng 10; hoàn thành phiếu đánh giá kết quả tháng 9</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>N1_611 - Tổ chức, điều hành, đánh giá kết quả thực hiện nhiệm vụ của công chức thuộc phòng</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>Phiếu đánh giá kết quả thực hiện nhiệm vụ tháng 9/2026 có xác nhận TCM</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="n"/>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="9" t="n"/>
-      <c r="E46" s="9" t="n"/>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="10" t="n"/>
+      <c r="A46" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Rà soát, cập nhật hồ sơ chuyên môn cá nhân: giáo án, kế hoạch dạy học, sổ ghi điểm theo đúng quy định của Sở GD&amp;ĐT</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>N2_1115 - Kế hoạch triển khai hoạt động chuyên môn</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Hồ sơ chuyên môn đầy đủ: giáo án, kế hoạch dạy học, sổ điểm</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="n"/>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="9" t="n"/>
-      <c r="F47" s="9" t="n"/>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="10" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="n"/>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="9" t="n"/>
-      <c r="E48" s="9" t="n"/>
-      <c r="F48" s="9" t="n"/>
-      <c r="G48" s="9" t="n"/>
-      <c r="H48" s="10" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="n"/>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="9" t="n"/>
-      <c r="E49" s="9" t="n"/>
-      <c r="F49" s="9" t="n"/>
-      <c r="G49" s="9" t="n"/>
-      <c r="H49" s="10" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="n"/>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="9" t="n"/>
-      <c r="E50" s="9" t="n"/>
-      <c r="F50" s="9" t="n"/>
-      <c r="G50" s="9" t="n"/>
-      <c r="H50" s="10" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="n"/>
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="10" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="9" t="n"/>
-      <c r="F51" s="9" t="n"/>
-      <c r="G51" s="9" t="n"/>
-      <c r="H51" s="10" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="n"/>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="9" t="n"/>
-      <c r="G52" s="9" t="n"/>
-      <c r="H52" s="10" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="n"/>
-      <c r="B53" s="10" t="n"/>
-      <c r="C53" s="10" t="n"/>
-      <c r="D53" s="9" t="n"/>
-      <c r="E53" s="9" t="n"/>
-      <c r="F53" s="9" t="n"/>
-      <c r="G53" s="9" t="n"/>
-      <c r="H53" s="10" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="n"/>
-      <c r="B54" s="10" t="n"/>
-      <c r="C54" s="10" t="n"/>
-      <c r="D54" s="9" t="n"/>
-      <c r="E54" s="9" t="n"/>
-      <c r="F54" s="9" t="n"/>
-      <c r="G54" s="9" t="n"/>
-      <c r="H54" s="10" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="n"/>
-      <c r="B55" s="10" t="n"/>
-      <c r="C55" s="10" t="n"/>
-      <c r="D55" s="9" t="n"/>
-      <c r="E55" s="9" t="n"/>
-      <c r="F55" s="9" t="n"/>
-      <c r="G55" s="9" t="n"/>
-      <c r="H55" s="10" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="9" t="n"/>
-      <c r="B56" s="10" t="n"/>
-      <c r="C56" s="10" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
-      <c r="H56" s="10" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="9" t="n"/>
-      <c r="E57" s="9" t="n"/>
-      <c r="F57" s="9" t="n"/>
-      <c r="G57" s="9" t="n"/>
-      <c r="H57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="n"/>
-      <c r="B58" s="10" t="n"/>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="9" t="n"/>
-      <c r="E58" s="9" t="n"/>
-      <c r="F58" s="9" t="n"/>
-      <c r="G58" s="9" t="n"/>
-      <c r="H58" s="10" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="n"/>
-      <c r="B59" s="10" t="n"/>
-      <c r="C59" s="10" t="n"/>
-      <c r="D59" s="9" t="n"/>
-      <c r="E59" s="9" t="n"/>
-      <c r="F59" s="9" t="n"/>
-      <c r="G59" s="9" t="n"/>
-      <c r="H59" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="n"/>
-      <c r="B60" s="10" t="n"/>
-      <c r="C60" s="10" t="n"/>
-      <c r="D60" s="9" t="n"/>
-      <c r="E60" s="9" t="n"/>
-      <c r="F60" s="9" t="n"/>
-      <c r="G60" s="9" t="n"/>
-      <c r="H60" s="10" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="9" t="n"/>
-      <c r="B61" s="10" t="n"/>
-      <c r="C61" s="10" t="n"/>
-      <c r="D61" s="9" t="n"/>
-      <c r="E61" s="9" t="n"/>
-      <c r="F61" s="9" t="n"/>
-      <c r="G61" s="9" t="n"/>
-      <c r="H61" s="10" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="n"/>
-      <c r="B62" s="10" t="n"/>
-      <c r="C62" s="10" t="n"/>
-      <c r="D62" s="9" t="n"/>
-      <c r="E62" s="9" t="n"/>
-      <c r="F62" s="9" t="n"/>
-      <c r="G62" s="9" t="n"/>
-      <c r="H62" s="10" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="n"/>
-      <c r="B63" s="10" t="n"/>
-      <c r="C63" s="10" t="n"/>
-      <c r="D63" s="9" t="n"/>
-      <c r="E63" s="9" t="n"/>
-      <c r="F63" s="9" t="n"/>
-      <c r="G63" s="9" t="n"/>
-      <c r="H63" s="10" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="9" t="n"/>
-      <c r="B64" s="10" t="n"/>
-      <c r="C64" s="10" t="n"/>
-      <c r="D64" s="9" t="n"/>
-      <c r="E64" s="9" t="n"/>
-      <c r="F64" s="9" t="n"/>
-      <c r="G64" s="9" t="n"/>
-      <c r="H64" s="10" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="9" t="n"/>
-      <c r="B65" s="10" t="n"/>
-      <c r="C65" s="10" t="n"/>
-      <c r="D65" s="9" t="n"/>
-      <c r="E65" s="9" t="n"/>
-      <c r="F65" s="9" t="n"/>
-      <c r="G65" s="9" t="n"/>
-      <c r="H65" s="10" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="9" t="n"/>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="9" t="n"/>
-      <c r="E66" s="9" t="n"/>
-      <c r="F66" s="9" t="n"/>
-      <c r="G66" s="9" t="n"/>
-      <c r="H66" s="10" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="9" t="n"/>
-      <c r="B67" s="10" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="9" t="n"/>
-      <c r="E67" s="9" t="n"/>
-      <c r="F67" s="9" t="n"/>
-      <c r="G67" s="9" t="n"/>
-      <c r="H67" s="10" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="9" t="n"/>
-      <c r="B68" s="10" t="n"/>
-      <c r="C68" s="10" t="n"/>
-      <c r="D68" s="9" t="n"/>
-      <c r="E68" s="9" t="n"/>
-      <c r="F68" s="9" t="n"/>
-      <c r="G68" s="9" t="n"/>
-      <c r="H68" s="10" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="9" t="n"/>
-      <c r="B69" s="10" t="n"/>
-      <c r="C69" s="10" t="n"/>
-      <c r="D69" s="9" t="n"/>
-      <c r="E69" s="9" t="n"/>
-      <c r="F69" s="9" t="n"/>
-      <c r="G69" s="9" t="n"/>
-      <c r="H69" s="10" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="9" t="n"/>
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="10" t="n"/>
-      <c r="D70" s="9" t="n"/>
-      <c r="E70" s="9" t="n"/>
-      <c r="F70" s="9" t="n"/>
-      <c r="G70" s="9" t="n"/>
-      <c r="H70" s="10" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="n"/>
-      <c r="B71" s="10" t="n"/>
-      <c r="C71" s="10" t="n"/>
-      <c r="D71" s="9" t="n"/>
-      <c r="E71" s="9" t="n"/>
-      <c r="F71" s="9" t="n"/>
-      <c r="G71" s="9" t="n"/>
-      <c r="H71" s="10" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="9" t="n"/>
-      <c r="B72" s="10" t="n"/>
-      <c r="C72" s="10" t="n"/>
-      <c r="D72" s="9" t="n"/>
-      <c r="E72" s="9" t="n"/>
-      <c r="F72" s="9" t="n"/>
-      <c r="G72" s="9" t="n"/>
-      <c r="H72" s="10" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="n"/>
-      <c r="B73" s="10" t="n"/>
-      <c r="C73" s="10" t="n"/>
-      <c r="D73" s="9" t="n"/>
-      <c r="E73" s="9" t="n"/>
-      <c r="F73" s="9" t="n"/>
-      <c r="G73" s="9" t="n"/>
-      <c r="H73" s="10" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="9" t="n"/>
-      <c r="B74" s="10" t="n"/>
-      <c r="C74" s="10" t="n"/>
-      <c r="D74" s="9" t="n"/>
-      <c r="E74" s="9" t="n"/>
-      <c r="F74" s="9" t="n"/>
-      <c r="G74" s="9" t="n"/>
-      <c r="H74" s="10" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="9" t="n"/>
-      <c r="B75" s="10" t="n"/>
-      <c r="C75" s="10" t="n"/>
-      <c r="D75" s="9" t="n"/>
-      <c r="E75" s="9" t="n"/>
-      <c r="F75" s="9" t="n"/>
-      <c r="G75" s="9" t="n"/>
-      <c r="H75" s="10" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="9" t="n"/>
-      <c r="B76" s="10" t="n"/>
-      <c r="C76" s="10" t="n"/>
-      <c r="D76" s="9" t="n"/>
-      <c r="E76" s="9" t="n"/>
-      <c r="F76" s="9" t="n"/>
-      <c r="G76" s="9" t="n"/>
-      <c r="H76" s="10" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="9" t="n"/>
-      <c r="B77" s="10" t="n"/>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="9" t="n"/>
-      <c r="E77" s="9" t="n"/>
-      <c r="F77" s="9" t="n"/>
-      <c r="G77" s="9" t="n"/>
-      <c r="H77" s="10" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="9" t="n"/>
-      <c r="B78" s="10" t="n"/>
-      <c r="C78" s="10" t="n"/>
-      <c r="D78" s="9" t="n"/>
-      <c r="E78" s="9" t="n"/>
-      <c r="F78" s="9" t="n"/>
-      <c r="G78" s="9" t="n"/>
-      <c r="H78" s="10" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="9" t="n"/>
-      <c r="B79" s="10" t="n"/>
-      <c r="C79" s="10" t="n"/>
-      <c r="D79" s="9" t="n"/>
-      <c r="E79" s="9" t="n"/>
-      <c r="F79" s="9" t="n"/>
-      <c r="G79" s="9" t="n"/>
-      <c r="H79" s="10" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="9" t="n"/>
-      <c r="B80" s="10" t="n"/>
-      <c r="C80" s="10" t="n"/>
-      <c r="D80" s="9" t="n"/>
-      <c r="E80" s="9" t="n"/>
-      <c r="F80" s="9" t="n"/>
-      <c r="G80" s="9" t="n"/>
-      <c r="H80" s="10" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="9" t="n"/>
-      <c r="B81" s="10" t="n"/>
-      <c r="C81" s="10" t="n"/>
-      <c r="D81" s="9" t="n"/>
-      <c r="E81" s="9" t="n"/>
-      <c r="F81" s="9" t="n"/>
-      <c r="G81" s="9" t="n"/>
-      <c r="H81" s="10" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="9" t="n"/>
-      <c r="B82" s="10" t="n"/>
-      <c r="C82" s="10" t="n"/>
-      <c r="D82" s="9" t="n"/>
-      <c r="E82" s="9" t="n"/>
-      <c r="F82" s="9" t="n"/>
-      <c r="G82" s="9" t="n"/>
-      <c r="H82" s="10" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="n"/>
-      <c r="B83" s="10" t="n"/>
-      <c r="C83" s="10" t="n"/>
-      <c r="D83" s="9" t="n"/>
-      <c r="E83" s="9" t="n"/>
-      <c r="F83" s="9" t="n"/>
-      <c r="G83" s="9" t="n"/>
-      <c r="H83" s="10" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="9" t="n"/>
-      <c r="B84" s="10" t="n"/>
-      <c r="C84" s="10" t="n"/>
-      <c r="D84" s="9" t="n"/>
-      <c r="E84" s="9" t="n"/>
-      <c r="F84" s="9" t="n"/>
-      <c r="G84" s="9" t="n"/>
-      <c r="H84" s="10" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="9" t="n"/>
-      <c r="B85" s="10" t="n"/>
-      <c r="C85" s="10" t="n"/>
-      <c r="D85" s="9" t="n"/>
-      <c r="E85" s="9" t="n"/>
-      <c r="F85" s="9" t="n"/>
-      <c r="G85" s="9" t="n"/>
-      <c r="H85" s="10" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="9" t="n"/>
-      <c r="B86" s="10" t="n"/>
-      <c r="C86" s="10" t="n"/>
-      <c r="D86" s="9" t="n"/>
-      <c r="E86" s="9" t="n"/>
-      <c r="F86" s="9" t="n"/>
-      <c r="G86" s="9" t="n"/>
-      <c r="H86" s="10" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="n"/>
-      <c r="B87" s="10" t="n"/>
-      <c r="C87" s="10" t="n"/>
-      <c r="D87" s="9" t="n"/>
-      <c r="E87" s="9" t="n"/>
-      <c r="F87" s="9" t="n"/>
-      <c r="G87" s="9" t="n"/>
-      <c r="H87" s="10" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="9" t="n"/>
-      <c r="B88" s="10" t="n"/>
-      <c r="C88" s="10" t="n"/>
-      <c r="D88" s="9" t="n"/>
-      <c r="E88" s="9" t="n"/>
-      <c r="F88" s="9" t="n"/>
-      <c r="G88" s="9" t="n"/>
-      <c r="H88" s="10" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="9" t="n"/>
-      <c r="B89" s="10" t="n"/>
-      <c r="C89" s="10" t="n"/>
-      <c r="D89" s="9" t="n"/>
-      <c r="E89" s="9" t="n"/>
-      <c r="F89" s="9" t="n"/>
-      <c r="G89" s="9" t="n"/>
-      <c r="H89" s="10" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="9" t="n"/>
-      <c r="B90" s="10" t="n"/>
-      <c r="C90" s="10" t="n"/>
-      <c r="D90" s="9" t="n"/>
-      <c r="E90" s="9" t="n"/>
-      <c r="F90" s="9" t="n"/>
-      <c r="G90" s="9" t="n"/>
-      <c r="H90" s="10" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="9" t="n"/>
-      <c r="B91" s="10" t="n"/>
-      <c r="C91" s="10" t="n"/>
-      <c r="D91" s="9" t="n"/>
-      <c r="E91" s="9" t="n"/>
-      <c r="F91" s="9" t="n"/>
-      <c r="G91" s="9" t="n"/>
-      <c r="H91" s="10" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="9" t="n"/>
-      <c r="B92" s="10" t="n"/>
-      <c r="C92" s="10" t="n"/>
-      <c r="D92" s="9" t="n"/>
-      <c r="E92" s="9" t="n"/>
-      <c r="F92" s="9" t="n"/>
-      <c r="G92" s="9" t="n"/>
-      <c r="H92" s="10" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="9" t="n"/>
-      <c r="B93" s="10" t="n"/>
-      <c r="C93" s="10" t="n"/>
-      <c r="D93" s="9" t="n"/>
-      <c r="E93" s="9" t="n"/>
-      <c r="F93" s="9" t="n"/>
-      <c r="G93" s="9" t="n"/>
-      <c r="H93" s="10" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="9" t="n"/>
-      <c r="B94" s="10" t="n"/>
-      <c r="C94" s="10" t="n"/>
-      <c r="D94" s="9" t="n"/>
-      <c r="E94" s="9" t="n"/>
-      <c r="F94" s="9" t="n"/>
-      <c r="G94" s="9" t="n"/>
-      <c r="H94" s="10" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="9" t="n"/>
-      <c r="B95" s="10" t="n"/>
-      <c r="C95" s="10" t="n"/>
-      <c r="D95" s="9" t="n"/>
-      <c r="E95" s="9" t="n"/>
-      <c r="F95" s="9" t="n"/>
-      <c r="G95" s="9" t="n"/>
-      <c r="H95" s="10" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="9" t="n"/>
-      <c r="B96" s="10" t="n"/>
-      <c r="C96" s="10" t="n"/>
-      <c r="D96" s="9" t="n"/>
-      <c r="E96" s="9" t="n"/>
-      <c r="F96" s="9" t="n"/>
-      <c r="G96" s="9" t="n"/>
-      <c r="H96" s="10" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="n"/>
-      <c r="B97" s="10" t="n"/>
-      <c r="C97" s="10" t="n"/>
-      <c r="D97" s="9" t="n"/>
-      <c r="E97" s="9" t="n"/>
-      <c r="F97" s="9" t="n"/>
-      <c r="G97" s="9" t="n"/>
-      <c r="H97" s="10" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="9" t="n"/>
-      <c r="B98" s="10" t="n"/>
-      <c r="C98" s="10" t="n"/>
-      <c r="D98" s="9" t="n"/>
-      <c r="E98" s="9" t="n"/>
-      <c r="F98" s="9" t="n"/>
-      <c r="G98" s="9" t="n"/>
-      <c r="H98" s="10" t="n"/>
-    </row>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
+      <c r="A47" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Tiến hành bước đầu thu thập tài liệu, nghiên cứu và xây dựng đề cương chi tiết Sáng kiến kinh nghiệm năm học 2026 - 2027</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>N3_658 - Thẩm định hồ sơ và tham mưu công tác sáng kiến, đề tài nghiên cứu khoa học; các cuộc thi về công tác học sinh sinh viên; hồ sơ b</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>Đề cương SKKN năm học 2026-2027 đã hoàn thiện bước đầu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:L2"/>
